--- a/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>CATO</t>
   </si>
@@ -656,405 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44044</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43953</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43862</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43771</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43680</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43589</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43498</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43407</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43225</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43134</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>182900</v>
+        <v>158300</v>
       </c>
       <c r="E8" s="3">
+        <v>374900</v>
+      </c>
+      <c r="F8" s="3">
         <v>192100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>179000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>176600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>403600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>206700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>176200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>172200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>420800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>213100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>155400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>150800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>268900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>190900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>191500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>442900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>230400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>192400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>190000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>447200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>238300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>213000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>190300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>446700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>239700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>220400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>117600</v>
+        <v>105800</v>
       </c>
       <c r="E9" s="3">
+        <v>239700</v>
+      </c>
+      <c r="F9" s="3">
         <v>122100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>121900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>123800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>264000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>132200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>109600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>239300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>123700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>107400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>109400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>216300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>83600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>123800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>118600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>266500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>136100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>127400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>123000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>272100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>142300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>141600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>124500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>287000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>145800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>155300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>65300</v>
+        <v>52500</v>
       </c>
       <c r="E10" s="3">
+        <v>135200</v>
+      </c>
+      <c r="F10" s="3">
         <v>70000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>57100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>139600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>181500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>89400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>48000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>52600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>67100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>72900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>176400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>94300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>65000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>67000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>175100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>96000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>71400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>65800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>159700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>93900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>65100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1281,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,20 +1319,20 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>3800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2300</v>
-      </c>
-      <c r="P14" s="3">
-        <v>5300</v>
       </c>
       <c r="Q14" s="3">
         <v>5300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>5300</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1329,8 +1349,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1353,8 +1373,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,88 +1385,91 @@
         <v>2500</v>
       </c>
       <c r="E15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F15" s="3">
         <v>2400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>3600</v>
       </c>
       <c r="O15" s="3">
         <v>3600</v>
       </c>
       <c r="P15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>7500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>4000</v>
       </c>
       <c r="R15" s="3">
         <v>4000</v>
       </c>
       <c r="S15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T15" s="3">
         <v>3800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>5000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>9900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>181700</v>
+        <v>170100</v>
       </c>
       <c r="E17" s="3">
+        <v>368100</v>
+      </c>
+      <c r="F17" s="3">
         <v>186400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>184500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>188000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>390800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>195400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>182800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>379700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>190000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>169200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>164900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>320300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>140100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>194800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>187100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>406200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>205900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>197300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>188900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>415300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>212500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>222400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>191600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>425000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>214600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>244100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>207200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1200</v>
+        <v>-11800</v>
       </c>
       <c r="E18" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F18" s="3">
         <v>5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-39400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>31900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>25800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>21700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>25100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,186 +1716,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2300</v>
       </c>
       <c r="H20" s="3">
         <v>2300</v>
       </c>
       <c r="I20" s="3">
-        <v>400</v>
+        <v>2300</v>
       </c>
       <c r="J20" s="3">
         <v>400</v>
       </c>
       <c r="K20" s="3">
+        <v>400</v>
+      </c>
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5000</v>
+        <v>-7800</v>
       </c>
       <c r="E21" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F21" s="3">
         <v>8900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>20700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-33500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>47300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>29400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>42500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>30800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>31100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1872,47 +1912,47 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -1920,163 +1960,169 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>200</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>15100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M23" s="3">
+        <v>42300</v>
+      </c>
+      <c r="N23" s="3">
+        <v>23800</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="T23" s="3">
+        <v>6000</v>
+      </c>
+      <c r="U23" s="3">
+        <v>39600</v>
+      </c>
+      <c r="V23" s="3">
+        <v>25600</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X23" s="3">
         <v>2500</v>
       </c>
-      <c r="E23" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>15100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>2900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>42300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>23800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-48600</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-37500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="S23" s="3">
-        <v>6000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>39600</v>
-      </c>
-      <c r="U23" s="3">
-        <v>25600</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>34100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>23900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1300</v>
+        <v>-4300</v>
       </c>
       <c r="E24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -2087,49 +2133,52 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1100</v>
+        <v>-6100</v>
       </c>
       <c r="E26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F26" s="3">
         <v>4400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-48600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-37500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>21300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>23400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>21400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>22200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1100</v>
+        <v>-5700</v>
       </c>
       <c r="E27" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F27" s="3">
         <v>4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>32000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>20600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>22800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>20900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2519,21 +2580,21 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>2600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>9700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>13000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>9100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2543,24 +2604,24 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>500</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +2818,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1300</v>
+        <v>-1500</v>
       </c>
       <c r="E32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-2300</v>
       </c>
       <c r="H32" s="3">
         <v>-2300</v>
       </c>
       <c r="I32" s="3">
-        <v>-400</v>
+        <v>-2300</v>
       </c>
       <c r="J32" s="3">
         <v>-400</v>
       </c>
       <c r="K32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1100</v>
+        <v>-5700</v>
       </c>
       <c r="E33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F33" s="3">
         <v>4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>32000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>20600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>22800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>20900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>21700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1100</v>
+        <v>-5700</v>
       </c>
       <c r="E35" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F35" s="3">
         <v>4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>32000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>20600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>22800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>20900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>21700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44044</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43953</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43862</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43771</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43680</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43589</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43498</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43407</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43225</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43134</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,542 +3353,561 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E41" s="3">
         <v>56000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>71500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>78000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>78700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>77700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>52400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>47200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E42" s="3">
         <v>77200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>87800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>108700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>128500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>123400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>120000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>146000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>176100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>191500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>160900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>126400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>132600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>118000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>200400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>203300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>207400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>174400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>182700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>183200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>187100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>147100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>118800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>136200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>159900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>178900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>201200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E43" s="3">
         <v>26900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>60100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>55800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>55100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>47700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>39000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>30500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>26100</v>
-      </c>
-      <c r="S43" s="3">
-        <v>27500</v>
       </c>
       <c r="T43" s="3">
         <v>27500</v>
       </c>
       <c r="U43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="V43" s="3">
         <v>29900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>28100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>37000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>34700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>37100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>28000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>29600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>32300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>98900</v>
+      </c>
+      <c r="E44" s="3">
         <v>92700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>106800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>112100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>116700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>127600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>124900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>90200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>72000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>84800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>84100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>84300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>88300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>122800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>115400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>114000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>100000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>111200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>119600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>113000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>104500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>107900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>121500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>127800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>106200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>131800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>145700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E45" s="3">
         <v>11000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>26000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>18200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>18300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>19300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E46" s="3">
         <v>263800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>273500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>277700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>298800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>305500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>343500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>355700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>361800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>349600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>333100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>290600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>294500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>280700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>311100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>362800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>374200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>369300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>360200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>370600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>374900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>378400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>378900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>372500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>393400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>391500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>413700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>443800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>442900</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,97 +3995,103 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E48" s="3">
         <v>212200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>229700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>244700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>210800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>222600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>235600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>244300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>196000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>212000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>255800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>272400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>266200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>286700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>298700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>289500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>242600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>254600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>271000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>94300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>99300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>102300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>105500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>109400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>120200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>122500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>124700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>126400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4068,8 +4179,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E52" s="3">
         <v>31700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>32700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>34300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>33000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>32700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>34400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>34100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>34200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>34800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>35000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>35200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>36100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>32700</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>487400</v>
+      </c>
+      <c r="E54" s="3">
         <v>507700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>534600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>553100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>540500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>560800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>612000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>633800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>587200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>590800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>617900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>591500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>590900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>596400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>641000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>685000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>651200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>657400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>665000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>497900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>506900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>515100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>518500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>516100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>548400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>549000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>573600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>606300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>617600</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,97 +4709,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E57" s="3">
         <v>84900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>88500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>92000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>95200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>91600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>106200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>109500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>71500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>82300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>73800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>75000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>54000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>68400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>67700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>66600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>84300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>72600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>74900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>82600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>88300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>74500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>83100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>105200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4706,18 +4840,18 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
         <v>30000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4733,8 +4867,8 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4757,186 +4891,195 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E59" s="3">
         <v>75500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>97100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>111000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>108300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>107700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>129500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>134600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>121400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>120300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>108200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>101700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>109600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>130900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>117700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>111900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>112800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>56800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>65500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>63500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>61800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>56500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>60800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>63000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>61000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>66700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>59300</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>184200</v>
+      </c>
+      <c r="E60" s="3">
         <v>160400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>185600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>203000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>203400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>199300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>235700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>244100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>214300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>201400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>202600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>181900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>176700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>154000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>184500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>199300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>186800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>179600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>179300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>141100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>138100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>138400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>130900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>139100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>149100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>137500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>144100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>171900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5024,97 +5167,103 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E62" s="3">
         <v>121700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>122200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>123600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>102300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>115700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>125600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>135400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>102000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>115600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>153500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>163000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>158000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>176200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>184800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>169200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>132700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>143100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>157200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>40000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>42600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>46300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>50600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>46800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>48900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>49700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>50500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>270100</v>
+      </c>
+      <c r="E66" s="3">
         <v>282100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>307900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>326500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>305700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>315000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>361400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>379600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>316400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>317000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>356000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>345000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>334700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>330200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>369300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>368500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>319500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>322700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>336500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>181100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>180700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>183800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>177200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>189700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>195900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>186400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>193800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>222400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>205900</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E72" s="3">
         <v>100800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>103400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>104700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>114800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>124800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>131200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>134200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>151200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>154900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>144400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>129300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>139800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>150900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>158000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>203500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>220200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>224500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>220800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>210500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>221800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>228100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>240400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>225900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>252600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>264000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>282800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>288000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217300</v>
+      </c>
+      <c r="E76" s="3">
         <v>225500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>226800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>226600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>234800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>245800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>250700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>254200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>270800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>273800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>261900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>246500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>256100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>266200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>271700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>316500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>331700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>334600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>328500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>316800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>326200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>331300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>341200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>326400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>352400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>362600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>379800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>383900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>411700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44044</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43953</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43862</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43771</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43680</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43589</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43498</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43407</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43225</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43134</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1100</v>
+        <v>-5700</v>
       </c>
       <c r="E81" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F81" s="3">
         <v>4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>32000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>20600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>22800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>20900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>21700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,8 +6806,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6617,88 +6816,91 @@
         <v>2500</v>
       </c>
       <c r="E83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>3600</v>
       </c>
       <c r="O83" s="3">
         <v>3600</v>
       </c>
       <c r="P83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>7500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>4000</v>
       </c>
       <c r="R83" s="3">
         <v>4000</v>
       </c>
       <c r="S83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T83" s="3">
         <v>3800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>11700</v>
+        <v>-9900</v>
       </c>
       <c r="E89" s="3">
+        <v>21600</v>
+      </c>
+      <c r="F89" s="3">
         <v>9900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>82000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-71300</v>
-      </c>
-      <c r="R89" s="3">
-        <v>4100</v>
       </c>
       <c r="S89" s="3">
         <v>4100</v>
       </c>
       <c r="T89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="U89" s="3">
         <v>45200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>56500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>31600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>43400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>25900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-8800</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-600</v>
       </c>
       <c r="M91" s="3">
         <v>-600</v>
       </c>
       <c r="N91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>8500</v>
+        <v>-17700</v>
       </c>
       <c r="E94" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F94" s="3">
         <v>15300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>15800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>13600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>91000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>76900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>7900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>13100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>21000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>33600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>18800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>4000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7662,55 +7896,55 @@
         <v>-3500</v>
       </c>
       <c r="E96" s="3">
-        <v>-3500</v>
+        <v>-7000</v>
       </c>
       <c r="F96" s="3">
         <v>-3500</v>
       </c>
       <c r="G96" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H96" s="3">
         <v>-3600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-7300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-3700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>100</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-8000</v>
       </c>
       <c r="Q96" s="3">
         <v>-8000</v>
       </c>
       <c r="R96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-8100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-8200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-16300</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-8100</v>
       </c>
       <c r="V96" s="3">
         <v>-8100</v>
@@ -7719,31 +7953,34 @@
         <v>-8100</v>
       </c>
       <c r="X96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-8200</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-8300</v>
       </c>
       <c r="AA96" s="3">
         <v>-8300</v>
       </c>
       <c r="AB96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8252,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3800</v>
+        <v>-3300</v>
       </c>
       <c r="E100" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-5600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>12400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-10800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-26300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-46500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8163,11 +8412,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8181,99 +8430,105 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>8</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>16400</v>
+        <v>-30900</v>
       </c>
       <c r="E102" s="3">
+        <v>36100</v>
+      </c>
+      <c r="F102" s="3">
         <v>19700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>30500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>CATO</t>
   </si>
@@ -656,418 +656,444 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F7" s="2">
         <v>45227</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45136</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45045</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44954</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44772</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44590</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44499</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44317</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44226</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44044</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43953</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43862</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43771</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43680</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43589</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43498</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43407</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43316</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43225</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43134</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43036</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42945</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42854</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42763</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>177100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>174900</v>
+      </c>
+      <c r="F8" s="3">
         <v>158300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>374900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>192100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>179000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>176600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>403600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>206700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>176200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>172200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>420800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>213100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>155400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>150800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>268900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>100700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>190900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>191500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>442900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>230400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>192400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>190000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>447200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>238300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>213000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>190300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>446700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>239700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>220400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>112500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>118800</v>
+      </c>
+      <c r="F9" s="3">
         <v>105800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>239700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>122100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>121900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>123800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>264000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>132200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>109600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>104200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>239300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>123700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>107400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>109400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>216300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>83600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>123800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>118600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>266500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>136100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>127400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>123000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>272100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>142300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>141600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>124500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>287000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>145800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>155300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>56100</v>
+      </c>
+      <c r="F10" s="3">
         <v>52500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>135200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>70000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>57100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>52800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>139600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>74500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>66600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>68000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>181500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>89400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>48000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>41400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>52600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>17100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>67100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>72900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>176400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>94300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>65000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>67000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>175100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>96000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>71400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>65800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>159700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>93900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>65100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1126,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,8 +1220,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,31 +1318,37 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1322,24 +1362,24 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>5300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>5300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1352,11 +1392,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1376,100 +1416,112 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G15" s="3">
         <v>4900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>5600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>3000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>6200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>3000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>3600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>3600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>7500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>4000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>4000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>3800</v>
-      </c>
-      <c r="U15" s="3">
-        <v>7700</v>
       </c>
       <c r="V15" s="3">
         <v>3800</v>
       </c>
       <c r="W15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="X15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>4000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>4100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>8400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>4200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>4700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>5000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>9900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>5100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>5600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1551,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>188700</v>
+      </c>
+      <c r="F17" s="3">
         <v>170100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>368100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>186400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>184500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>188000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>390800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>195400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>182800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>169900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>379700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>190000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>169200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>164900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>320300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>140100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>194800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>187100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>406200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>205900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>197300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>188900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>415300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>212500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>222400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>191600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>425000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>214600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>244100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>207200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-11800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-11400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>12800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>11300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>41100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>23100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-51400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-39400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>4400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>36700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>24500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-4900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>31900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>25800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>21700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>25100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,192 +1783,206 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1200</v>
       </c>
       <c r="N20" s="3">
         <v>600</v>
       </c>
       <c r="O20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P20" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>2200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>8900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>20700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>14400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>48500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>26800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-7100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-41100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-33500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>9900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>47300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>29400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>6600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>42500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>30800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>33900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>31100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1915,220 +1995,232 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>6600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-9100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>15100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>11700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>42300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>23800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-48600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-37500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>6000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>39600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>25600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>34100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>26600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>23900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>26100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F24" s="3">
         <v>-4300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-4700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>7600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>7600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -2136,49 +2228,55 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>6500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>4300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>4200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>3200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>3800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2367,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>7500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>8600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>34700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>20700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-48600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-37500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>6000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>33100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>21300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>29900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>23400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>21400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>22200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-12800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>7100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>9200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>8100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>32900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>19700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-47000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-36300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>5800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>32000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>20600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>29000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>22800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>2600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>20900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>21700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,31 +2661,37 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2583,51 +2705,51 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>2600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>9700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>13000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>9100</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>500</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2637,8 +2759,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2857,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,192 +2955,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1200</v>
       </c>
       <c r="N32" s="3">
         <v>-600</v>
       </c>
       <c r="O32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>7100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>9200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>8100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>32900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>19700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-7900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-34000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-27200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>5800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>32000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>20600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>29000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>22800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-15100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>2600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>20900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>21700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3249,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>7100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>9200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>8100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>32900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>19700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-7900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-34000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-27200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>5800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>32000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>20600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>29000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>22800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-15100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>2600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>20900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>21700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F38" s="2">
         <v>45227</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45136</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45045</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44954</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44772</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44590</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44499</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44317</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44226</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44044</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43953</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43862</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43771</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43680</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43589</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43498</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43407</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43316</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43225</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43134</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43036</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42945</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42854</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42763</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3490,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,560 +3526,598 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F41" s="3">
         <v>25000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>56000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>39600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>30200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>25900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>19800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>24000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>25400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>22300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>17500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>36600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>29800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>11800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>21200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>26000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>36500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>24600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>26700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>37800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>71500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>78000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>78700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>77700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>52400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>47200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>79000</v>
+      </c>
+      <c r="F42" s="3">
         <v>93600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>77200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>87800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>108700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>128500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>123400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>120000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>146000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>176100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>191500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>160900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>126400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>132600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>100400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>118000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>200400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>203300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>207400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>174400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>182700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>183200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>187100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>147100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>118800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>136200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>159900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>178900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>201200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F43" s="3">
         <v>31100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>26900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>28200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>26500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>25700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>24800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>60100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>55800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>56000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>51300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>55100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>52700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>47700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>39000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>30500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>26100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>27500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>27500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>29900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>28100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>37000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>34700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>37100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>28000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>30500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>29600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>32300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>30300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>101300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F44" s="3">
         <v>98900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>92700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>106800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>112100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>116700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>116600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>127600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>124900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>90200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>72000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>84800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>84100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>84300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>88300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>122800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>115400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>114000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>100000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>111200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>119600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>113000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>104500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>107900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>121500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>127800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>106200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>131800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>145700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F45" s="3">
         <v>12500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>11000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>11100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>10700</v>
       </c>
       <c r="I45" s="3">
         <v>10500</v>
       </c>
       <c r="J45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L45" s="3">
         <v>9900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>9200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>15400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>9300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>9900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>9800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>11100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>16400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>10000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>9100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>8200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>8500</v>
       </c>
       <c r="V45" s="3">
         <v>8200</v>
       </c>
       <c r="W45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="X45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Y45" s="3">
         <v>15600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>15000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>14300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>15300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>26000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>20300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>18200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>18300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>19300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>243100</v>
+      </c>
+      <c r="F46" s="3">
         <v>261100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>263800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>273500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>277700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>298800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>305500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>343500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>355700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>361800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>349600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>333100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>290600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>294500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>280700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>311100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>362800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>374200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>369300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>360200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>370600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>374900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>378400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>378900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>372500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>393400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>391500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>413700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>443800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>442900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3998,100 +4208,112 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>204200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>218700</v>
+      </c>
+      <c r="F48" s="3">
         <v>189900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>212200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>229700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>244700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>210800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>222600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>235600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>244300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>196000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>212000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>255800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>272400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>266200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>286700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>298700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>289500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>242600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>254600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>271000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>94300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>99300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>102300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>105500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>109400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>120200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>122500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>124700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>126400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4182,8 +4404,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4502,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,100 +4600,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F52" s="3">
         <v>36400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>31700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>31400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>30800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>30900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>32800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>32900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>33800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>29400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>29200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>29100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>28500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>30200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>29100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>31200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>32700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>34300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>33500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>33800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>33000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>32700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>34400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>34100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>34200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>34800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>35000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>35200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>36100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>32700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4796,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>477100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>486800</v>
+      </c>
+      <c r="F54" s="3">
         <v>487400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>507700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>534600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>553100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>540500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>560800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>612000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>633800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>587200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>590800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>617900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>591500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>590900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>596400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>641000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>685000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>651200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>657400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>665000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>497900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>506900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>515100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>518500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>516100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>548400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>549000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>573600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>606300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>617600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4934,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,100 +4970,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>87800</v>
+      </c>
+      <c r="F57" s="3">
         <v>86900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>84900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>88500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>92000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>95200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>91600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>106200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>109500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>92900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>71500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>82300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>73800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>75000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>54000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>44900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>68400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>69100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>67700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>66600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>84300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>72600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>74900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>69100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>82600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>88300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>74500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>83100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>105200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4843,21 +5111,21 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3">
         <v>30000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4870,11 +5138,11 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4894,192 +5162,210 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>100200</v>
+      </c>
+      <c r="F59" s="3">
         <v>97300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>75500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>97100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>111000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>108300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>107700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>129500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>134600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>121400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>129900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>120300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>108200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>101700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>100100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>109600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>130900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>117700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>111900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>112800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>56800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>65500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>63500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>61800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>56500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>60800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>63000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>61000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>66700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>59300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>188000</v>
+      </c>
+      <c r="F60" s="3">
         <v>184200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>160400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>185600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>203000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>203400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>199300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>235700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>244100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>214300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>201400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>202600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>181900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>176700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>154000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>184500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>199300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>186800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>179600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>179300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>141100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>138100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>138400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>130900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>139100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>149100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>137500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>144100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>171900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5170,100 +5456,112 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>106500</v>
+      </c>
+      <c r="F62" s="3">
         <v>85800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>121700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>122200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>123600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>102300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>115700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>125600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>135400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>102000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>115600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>153500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>163000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>158000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>176200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>184800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>169200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>132700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>143100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>157200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>40000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>42600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>45400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>46300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>50600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>46800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>48900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>49700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>50500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5652,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5750,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5848,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>280200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>294500</v>
+      </c>
+      <c r="F66" s="3">
         <v>270100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>282100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>307900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>326500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>305700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>315000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>361400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>379600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>316400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>317000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>356000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>345000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>334700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>330200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>369300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>368500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>319500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>322700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>336500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>181100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>180700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>183800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>177200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>189700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>195900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>186400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>193800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>222400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>205900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5986,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +6080,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6178,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6276,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6374,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F72" s="3">
         <v>91200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>100800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>103400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>104700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>114800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>124800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>131200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>134200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>151200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>154900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>144400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>129300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>139800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>150900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>158000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>203500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>220200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>224500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>220800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>210500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>221800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>228100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>240400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>225900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>252600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>264000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>282800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>288000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6570,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6668,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6766,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>192300</v>
+      </c>
+      <c r="F76" s="3">
         <v>217300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>225500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>226800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>226600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>234800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>245800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>250700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>254200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>270800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>273800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>261900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>246500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>256100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>266200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>271700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>316500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>331700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>334600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>328500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>316800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>326200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>331300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>341200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>326400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>352400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>362600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>379800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>383900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>411700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6962,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F80" s="2">
         <v>45227</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45136</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45045</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44954</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44772</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44590</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44499</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44317</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44226</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44044</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43953</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43862</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43771</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43680</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43589</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43498</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43407</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43316</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43225</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43134</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43036</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42945</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42854</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42763</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>7100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>9200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>8100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>32900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>19700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-7900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-34000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-27200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>5800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>32000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>20600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>29000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>22800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-15100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>2600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>20900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>21700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7203,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G83" s="3">
         <v>4900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>3000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>6200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>3000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>3600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>4000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>4000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>3800</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7700</v>
       </c>
       <c r="V83" s="3">
         <v>3800</v>
       </c>
       <c r="W83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="X83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y83" s="3">
         <v>4000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>4100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>8400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>4200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>4700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>5000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>9900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>5100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>5600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7395,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7493,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7591,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7689,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7787,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-9900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>21600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>9900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>17000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-19600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>82000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>44500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>22200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-48200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-71300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>4100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>45200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>14700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>6000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>56500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>31600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>43400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>15600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>25900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-8800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7925,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1800</v>
+        <v>-3300</v>
       </c>
       <c r="E91" s="3">
         <v>-2300</v>
       </c>
       <c r="F91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H91" s="3">
         <v>-6200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-9800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +8117,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +8215,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-17700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>23800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>15300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>15800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-9900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>10100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>19600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>13600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-64900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-34200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>6600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>91000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>76900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-23400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>7900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-3100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>1800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>13100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>21000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>33600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>18800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>4000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,8 +8353,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7896,91 +8364,97 @@
         <v>-3500</v>
       </c>
       <c r="E96" s="3">
-        <v>-7000</v>
+        <v>-3500</v>
       </c>
       <c r="F96" s="3">
         <v>-3500</v>
       </c>
       <c r="G96" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-3500</v>
       </c>
-      <c r="H96" s="3">
-        <v>-3600</v>
-      </c>
       <c r="I96" s="3">
-        <v>-7300</v>
+        <v>-3500</v>
       </c>
       <c r="J96" s="3">
         <v>-3600</v>
       </c>
       <c r="K96" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M96" s="3">
         <v>-3700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-3800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-2500</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-8000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-8000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-8100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-8200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-16300</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-8100</v>
       </c>
       <c r="X96" s="3">
         <v>-8100</v>
       </c>
       <c r="Y96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-17200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8545,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8643,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,100 +8741,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-9300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-7100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-5400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-16700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-12700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-10500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-12400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-8800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-17600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>12400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-12600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-10100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-18800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-10700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-8100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-26300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-11400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-46500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8415,14 +8913,14 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8433,102 +8931,114 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-30900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>36100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>19700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-13100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>10400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>25200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>18000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-9000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-4800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>11900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-39800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>30500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>5600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>14500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-10300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>CATO</t>
   </si>
@@ -656,444 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E7" s="2">
         <v>45416</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43862</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43771</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43680</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43589</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43498</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43407</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43316</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43225</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43134</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E8" s="3">
         <v>177100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>174900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>158300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>374900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>192100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>179000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>176600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>403600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>206700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>176200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>172200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>420800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>213100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>155400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>150800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>268900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>190900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>191500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>442900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>230400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>192400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>190000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>447200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>238300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>213000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>190300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>446700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>239700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>220400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E9" s="3">
         <v>112500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>118800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>105800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>239700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>122100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>121900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>123800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>264000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>132200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>109600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>239300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>123700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>107400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>109400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>216300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>83600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>123800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>118600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>266500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>136100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>127400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>123000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>272100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>142300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>141600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>124500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>287000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>145800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>155300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E10" s="3">
         <v>64600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>135200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>70000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>57100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>52800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>139600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>181500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>89400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>48000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>41400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>52600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>17100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>67100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>72900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>176400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>94300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>65000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>67000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>175100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>96000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>71400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>65800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>159700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>93900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>65100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1128,8 +1141,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,8 +1240,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,8 +1341,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1350,8 +1370,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1368,20 +1388,20 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>3800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2300</v>
-      </c>
-      <c r="S14" s="3">
-        <v>5300</v>
       </c>
       <c r="T14" s="3">
         <v>5300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>5300</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1398,8 +1418,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1422,106 +1442,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>2000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2500</v>
       </c>
       <c r="F15" s="3">
         <v>2500</v>
       </c>
       <c r="G15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H15" s="3">
         <v>4900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>3600</v>
       </c>
       <c r="R15" s="3">
         <v>3600</v>
       </c>
       <c r="S15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T15" s="3">
         <v>7500</v>
-      </c>
-      <c r="T15" s="3">
-        <v>4000</v>
       </c>
       <c r="U15" s="3">
         <v>4000</v>
       </c>
       <c r="V15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W15" s="3">
         <v>3800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>7700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>8400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>9900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1553,204 +1579,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>169600</v>
+      </c>
+      <c r="E17" s="3">
         <v>171300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>188700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>170100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>368100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>186400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>184500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>188000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>390800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>195400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>182800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>169900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>379700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>190000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>169200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>164900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>320300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>140100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>194800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>187100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>406200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>205900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>197300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>188900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>415300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>212500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>222400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>191600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>425000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>214600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>244100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>207200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>41100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-51400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-39400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>36700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>31900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>25800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>21700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>25100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-23700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1785,204 +1818,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>5800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2300</v>
       </c>
       <c r="K20" s="3">
         <v>2300</v>
       </c>
       <c r="L20" s="3">
-        <v>400</v>
+        <v>2300</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
       </c>
       <c r="N20" s="3">
+        <v>400</v>
+      </c>
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E21" s="3">
         <v>13700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>48500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-41100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-33500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>47300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>29400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>30800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>33900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>31100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-16600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2001,47 +2041,47 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
@@ -2049,136 +2089,142 @@
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="3">
         <v>200</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
         <v>11600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>23800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-48600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-37500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>39600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>34100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>26600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>23900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>26100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2186,44 +2232,44 @@
         <v>600</v>
       </c>
       <c r="E24" s="3">
+        <v>600</v>
+      </c>
+      <c r="F24" s="3">
         <v>10900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2234,49 +2280,52 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2373,204 +2422,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>11000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-48600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-37500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>33100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>21300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>29900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>21400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-12800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>10400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-47000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>20600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>29000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>22800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2667,8 +2725,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2693,8 +2754,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2711,21 +2772,21 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>2600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>9700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>13000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>9100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2735,24 +2796,24 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>500</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-12300</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2765,8 +2826,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2863,8 +2927,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2961,204 +3028,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2300</v>
       </c>
       <c r="K32" s="3">
         <v>-2300</v>
       </c>
       <c r="L32" s="3">
-        <v>-400</v>
+        <v>-2300</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
       </c>
       <c r="N32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>10400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-27200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>20600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>29000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>22800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-15100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>21700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3255,209 +3331,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>10400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-27200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>20600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>29000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>22800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-15100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>21700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E38" s="2">
         <v>45416</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43862</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43771</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43680</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43589</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43498</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43407</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43316</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43225</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43134</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3492,8 +3577,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3528,596 +3614,615 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E41" s="3">
         <v>39100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>39600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>36500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>26700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>37800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>71500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>78000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>78700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>77700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>52400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>47200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E42" s="3">
         <v>66300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>79000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>93600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>77200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>87800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>108700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>128500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>123400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>120000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>146000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>176100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>191500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>160900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>126400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>132600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>100400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>118000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>200400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>203300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>207400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>174400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>182700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>183200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>187100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>147100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>118800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>136200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>159900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>178900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>201200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E43" s="3">
         <v>31700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>60100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>55800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>56000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>55100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>52700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>47700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>39000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>30500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26100</v>
-      </c>
-      <c r="V43" s="3">
-        <v>27500</v>
       </c>
       <c r="W43" s="3">
         <v>27500</v>
       </c>
       <c r="X43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="Y43" s="3">
         <v>29900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>28100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>37000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>34700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>37100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>28000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>29600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>32300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>30300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E44" s="3">
         <v>101300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>98600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>92700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>106800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>112100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>116600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>127600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>124900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>90200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>72000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>84800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>84100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>84300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>88300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>122800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>115400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>114000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>100000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>111200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>119600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>113000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>104500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>107900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>121500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>127800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>106200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>131800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>145700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E45" s="3">
         <v>11300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>26000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>18200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>18300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>19300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>243500</v>
+      </c>
+      <c r="E46" s="3">
         <v>249600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>261100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>263800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>273500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>277700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>298800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>305500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>343500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>355700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>361800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>349600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>333100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>290600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>294500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>280700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>311100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>362800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>374200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>369300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>360200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>370600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>374900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>378400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>378900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>372500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>393400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>391500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>413700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>443800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>442900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4214,106 +4319,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E48" s="3">
         <v>204200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>218700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>189900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>212200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>229700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>244700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>210800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>222600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>235600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>244300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>196000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>212000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>255800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>272400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>266200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>286700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>298700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>289500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>242600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>254600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>271000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>94300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>99300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>102300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>105500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>109400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>120200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>122500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>124700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>126400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4410,8 +4521,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4508,8 +4622,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4606,106 +4723,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E52" s="3">
         <v>23300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>33800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>32700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>34300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>33500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>32700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>34400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>34100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>34200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>34800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>35000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>35200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>36100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>32700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4802,106 +4925,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>455600</v>
+      </c>
+      <c r="E54" s="3">
         <v>477100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>486800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>487400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>507700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>534600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>553100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>540500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>560800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>612000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>633800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>587200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>590800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>617900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>591500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>590900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>596400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>641000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>685000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>651200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>657400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>665000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>497900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>506900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>515100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>518500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>516100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>548400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>549000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>573600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>606300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>617600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4936,8 +5065,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4972,106 +5102,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E57" s="3">
         <v>87000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>86900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>84900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>88500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>95200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>91600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>106200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>109500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>92900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>71500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>82300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>73800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>75000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>54000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>44900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>68400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>69100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>67700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>66600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>84300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>72600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>74900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>69100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>82600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>88300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>74500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>83100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>105200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5117,18 +5251,18 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3">
         <v>30000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5144,8 +5278,8 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5168,204 +5302,213 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E59" s="3">
         <v>96800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>97300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>75500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>97100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>111000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>108300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>107700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>134600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>121400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>129900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>120300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>108200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>101700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>100100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>109600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>130900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>117700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>111900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>112800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>56800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>65500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>63500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>61800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>56500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>60800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>63000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>61000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>66700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>59300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E60" s="3">
         <v>183800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>188000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>184200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>160400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>185600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>203000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>203400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>199300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>235700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>244100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>214300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>201400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>202600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>181900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>176700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>154000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>184500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>199300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>186800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>179600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>179300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>141100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>138100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>138400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>130900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>139100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>149100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>137500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>144100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>171900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5462,106 +5605,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E62" s="3">
         <v>96400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>106500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>85800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>121700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>122200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>123600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>102300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>115700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>125600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>135400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>102000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>115600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>153500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>163000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>158000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>176200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>184800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>169200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>132700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>143100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>157200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>40000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>45400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>46300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>50600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>46800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>48900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>49700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>50500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5658,8 +5807,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5756,8 +5908,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5854,106 +6009,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>260500</v>
+      </c>
+      <c r="E66" s="3">
         <v>280200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>294500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>270100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>282100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>307900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>326500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>305700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>315000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>361400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>379600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>316400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>317000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>356000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>345000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>334700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>330200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>369300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>368500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>319500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>322700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>336500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>181100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>180700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>183800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>177200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>189700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>195900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>186400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>193800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>222400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>205900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5988,8 +6149,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6086,8 +6248,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6184,8 +6349,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6282,8 +6450,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6380,106 +6551,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E72" s="3">
         <v>69500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>91200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>100800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>103400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>104700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>114800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>124800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>131200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>134200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>151200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>154900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>144400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>129300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>139800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>150900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>158000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>203500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>220200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>224500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>220800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>210500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>221800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>228100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>240400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>225900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>252600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>264000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>282800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>288000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6576,8 +6753,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6674,8 +6854,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6772,106 +6955,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>195100</v>
+      </c>
+      <c r="E76" s="3">
         <v>196900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>192300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>217300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>225500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>226800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>226600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>234800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>245800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>250700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>254200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>270800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>273800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>261900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>246500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>256100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>266200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>271700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>316500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>331700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>334600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>328500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>316800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>326200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>331300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>341200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>326400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>352400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>362600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>379800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>383900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>411700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6968,209 +7157,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E80" s="2">
         <v>45416</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43862</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43771</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43680</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43589</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43498</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43407</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43316</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43225</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43134</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>10400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-27200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>20600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>29000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>22800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-15100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>21700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7205,106 +7403,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2500</v>
       </c>
       <c r="F83" s="3">
         <v>2500</v>
       </c>
       <c r="G83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3600</v>
       </c>
       <c r="R83" s="3">
         <v>3600</v>
       </c>
       <c r="S83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T83" s="3">
         <v>7500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>4000</v>
       </c>
       <c r="U83" s="3">
         <v>4000</v>
       </c>
       <c r="V83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W83" s="3">
         <v>3800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7401,8 +7603,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7499,8 +7704,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7597,8 +7805,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7695,8 +7906,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7793,106 +8007,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E89" s="3">
         <v>5700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>82000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-48200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-71300</v>
-      </c>
-      <c r="U89" s="3">
-        <v>4100</v>
       </c>
       <c r="V89" s="3">
         <v>4100</v>
       </c>
       <c r="W89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X89" s="3">
         <v>45200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>56500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>31600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>43400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>15600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>25900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-8800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7927,106 +8147,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-600</v>
       </c>
       <c r="P91" s="3">
         <v>-600</v>
       </c>
       <c r="Q91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R91" s="3">
         <v>-2700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-700</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8123,8 +8347,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8221,106 +8448,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E94" s="3">
         <v>14600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>23800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>25900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>13600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-33100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>91000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>76900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>7900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-69900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>13100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>21000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>33600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>18800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>4000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8355,8 +8588,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8370,58 +8604,58 @@
         <v>-3500</v>
       </c>
       <c r="G96" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-3500</v>
       </c>
       <c r="I96" s="3">
         <v>-3500</v>
       </c>
       <c r="J96" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-7300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>100</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-8000</v>
       </c>
       <c r="T96" s="3">
         <v>-8000</v>
       </c>
       <c r="U96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-8100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-8200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-16300</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-8100</v>
       </c>
       <c r="Y96" s="3">
         <v>-8100</v>
@@ -8430,31 +8664,34 @@
         <v>-8100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-8200</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-8300</v>
       </c>
       <c r="AD96" s="3">
         <v>-8300</v>
       </c>
       <c r="AE96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-17200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8551,8 +8788,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8649,8 +8889,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8747,106 +8990,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>12400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-10100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-18800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-26300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-46500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8919,11 +9168,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8937,108 +9186,114 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>8</v>
+      <c r="AG101" s="3">
+        <v>0</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E102" s="3">
         <v>14700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-39800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>30500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>CATO</t>
   </si>
@@ -656,457 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E7" s="2">
         <v>45507</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45416</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45325</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43862</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43771</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43680</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43589</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43498</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43407</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43316</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43225</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43134</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>146200</v>
+      </c>
+      <c r="E8" s="3">
         <v>168600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>177100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>174900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>158300</v>
       </c>
-      <c r="H8" s="3">
-        <v>374900</v>
-      </c>
       <c r="I8" s="3">
+        <v>182900</v>
+      </c>
+      <c r="J8" s="3">
         <v>192100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>179000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>176600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>403600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>206700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>176200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>172200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>420800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>213100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>155400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>150800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>268900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>190900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>191500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>442900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>230400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>192400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>190000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>447200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>238300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>213000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>190300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>446700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>239700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>220400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E9" s="3">
         <v>109100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>112500</v>
       </c>
-      <c r="F9" s="3">
-        <v>118800</v>
-      </c>
       <c r="G9" s="3">
+        <v>117100</v>
+      </c>
+      <c r="H9" s="3">
         <v>105800</v>
       </c>
-      <c r="H9" s="3">
-        <v>239700</v>
-      </c>
       <c r="I9" s="3">
+        <v>117600</v>
+      </c>
+      <c r="J9" s="3">
         <v>122100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>121900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>123800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>264000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>132200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>109600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>239300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>123700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>107400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>109400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>216300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>83600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>123800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>118600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>266500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>136100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>127400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>123000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>272100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>142300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>141600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>124500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>287000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>145800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>155300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>59500</v>
+        <v>42800</v>
       </c>
       <c r="E10" s="3">
-        <v>64600</v>
+        <v>59100</v>
       </c>
       <c r="F10" s="3">
-        <v>56100</v>
+        <v>64200</v>
       </c>
       <c r="G10" s="3">
-        <v>52500</v>
+        <v>57300</v>
       </c>
       <c r="H10" s="3">
-        <v>135200</v>
+        <v>52000</v>
       </c>
       <c r="I10" s="3">
-        <v>70000</v>
+        <v>64800</v>
       </c>
       <c r="J10" s="3">
+        <v>69500</v>
+      </c>
+      <c r="K10" s="3">
         <v>57100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>52800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>139600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>181500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>89400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>48000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>41400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>17100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>67100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>176400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>94300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>65000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>67000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>175100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>96000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>71400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>65800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>159700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>93900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>65100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1243,8 +1256,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,37 +1360,40 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-3200</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1391,20 +1410,20 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>3800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2300</v>
-      </c>
-      <c r="T14" s="3">
-        <v>5300</v>
       </c>
       <c r="U14" s="3">
         <v>5300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>5300</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1421,8 +1440,8 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1445,109 +1464,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2500</v>
       </c>
       <c r="G15" s="3">
         <v>2500</v>
       </c>
       <c r="H15" s="3">
-        <v>4900</v>
+        <v>2500</v>
       </c>
       <c r="I15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J15" s="3">
         <v>2400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>3600</v>
       </c>
       <c r="S15" s="3">
         <v>3600</v>
       </c>
       <c r="T15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="U15" s="3">
         <v>7500</v>
-      </c>
-      <c r="U15" s="3">
-        <v>4000</v>
       </c>
       <c r="V15" s="3">
         <v>4000</v>
       </c>
       <c r="W15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X15" s="3">
         <v>3800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>7700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>9900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>5100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,210 +1605,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E17" s="3">
         <v>169600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>171300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>188700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>170100</v>
       </c>
-      <c r="H17" s="3">
-        <v>368100</v>
-      </c>
       <c r="I17" s="3">
+        <v>181700</v>
+      </c>
+      <c r="J17" s="3">
         <v>186400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>184500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>188000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>390800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>195400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>182800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>169900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>379700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>190000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>169200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>164900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>320300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>140100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>194800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>187100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>406200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>205900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>197300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>188900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>415300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>212500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>222400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>191600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>425000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>214600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>244100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>207200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-11800</v>
-      </c>
       <c r="H18" s="3">
-        <v>6800</v>
+        <v>-11900</v>
       </c>
       <c r="I18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J18" s="3">
         <v>5700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>41100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-51400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-39400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>36700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>31900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>25800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>21700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>25100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-23700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1819,210 +1851,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5800</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>800</v>
-      </c>
-      <c r="J20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>1400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2300</v>
       </c>
       <c r="L20" s="3">
         <v>2300</v>
       </c>
       <c r="M20" s="3">
-        <v>400</v>
+        <v>2300</v>
       </c>
       <c r="N20" s="3">
         <v>400</v>
       </c>
       <c r="O20" s="3">
+        <v>400</v>
+      </c>
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3100</v>
+        <v>-14700</v>
       </c>
       <c r="E21" s="3">
-        <v>13700</v>
+        <v>1300</v>
       </c>
       <c r="F21" s="3">
-        <v>-10000</v>
+        <v>7800</v>
       </c>
       <c r="G21" s="3">
-        <v>-7800</v>
+        <v>-10200</v>
       </c>
       <c r="H21" s="3">
-        <v>13900</v>
+        <v>-9400</v>
       </c>
       <c r="I21" s="3">
-        <v>8900</v>
+        <v>3600</v>
       </c>
       <c r="J21" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>48500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-41100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-33500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>47300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>29400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>42500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>30800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>33900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>31100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-16600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2035,8 +2074,8 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
@@ -2044,47 +2083,47 @@
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -2092,187 +2131,193 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI22" s="3">
         <v>200</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10300</v>
       </c>
-      <c r="H23" s="3">
-        <v>9000</v>
-      </c>
       <c r="I23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J23" s="3">
         <v>6600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>42300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>23800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-48600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-37500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>25600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>34100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>23900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>26100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>600</v>
       </c>
       <c r="F24" s="3">
+        <v>600</v>
+      </c>
+      <c r="G24" s="3">
         <v>10900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4300</v>
       </c>
-      <c r="H24" s="3">
-        <v>3500</v>
-      </c>
       <c r="I24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2283,49 +2328,52 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2425,210 +2473,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6100</v>
       </c>
-      <c r="H26" s="3">
-        <v>5600</v>
-      </c>
       <c r="I26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J26" s="3">
         <v>4400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-48600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-37500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>33100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>21300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>29900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
-        <v>5300</v>
-      </c>
       <c r="I27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J27" s="3">
         <v>4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-47000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-36300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>32000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>20600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>29000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>22800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>21700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2728,8 +2785,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2757,8 +2817,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2775,21 +2835,21 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>2600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>9700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>13000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>9100</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2799,24 +2859,24 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>500</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2829,8 +2889,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2930,8 +2993,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3031,210 +3097,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-5800</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-2300</v>
       </c>
       <c r="L32" s="3">
         <v>-2300</v>
       </c>
       <c r="M32" s="3">
-        <v>-400</v>
+        <v>-2300</v>
       </c>
       <c r="N32" s="3">
         <v>-400</v>
       </c>
       <c r="O32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
-        <v>10400</v>
-      </c>
       <c r="F33" s="3">
-        <v>-22100</v>
+        <v>11000</v>
       </c>
       <c r="G33" s="3">
-        <v>-5700</v>
+        <v>-23400</v>
       </c>
       <c r="H33" s="3">
-        <v>5300</v>
+        <v>-6100</v>
       </c>
       <c r="I33" s="3">
-        <v>4200</v>
+        <v>1100</v>
       </c>
       <c r="J33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-27200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>32000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>20600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>29000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-15100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>21700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3334,215 +3409,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
-        <v>10400</v>
-      </c>
       <c r="F35" s="3">
-        <v>-22100</v>
+        <v>11000</v>
       </c>
       <c r="G35" s="3">
-        <v>-5700</v>
+        <v>-23400</v>
       </c>
       <c r="H35" s="3">
-        <v>5300</v>
+        <v>-6100</v>
       </c>
       <c r="I35" s="3">
-        <v>4200</v>
+        <v>1100</v>
       </c>
       <c r="J35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-27200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>32000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>20600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>29000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-15100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>21700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E38" s="2">
         <v>45507</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45416</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45325</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43862</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43771</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43680</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43589</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43498</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43407</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43316</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43225</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43134</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3578,8 +3662,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3615,637 +3700,656 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E41" s="3">
         <v>30800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>56000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>18800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>36500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>24600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>26700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>37800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>71500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>78000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>78700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>77700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>52400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>47200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E42" s="3">
         <v>73900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>66300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>79000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>93600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>77200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>87800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>108700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>128500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>123400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>120000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>146000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>176100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>191500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>160900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>126400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>132600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>100400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>118000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>200400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>203300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>207400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>174400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>182700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>183200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>187100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>147100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>118800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>136200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>159900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>178900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>201200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E43" s="3">
         <v>29800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>31700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>60100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>51300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>55100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>52700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>47700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>39000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>30500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>27500</v>
       </c>
       <c r="X43" s="3">
         <v>27500</v>
       </c>
       <c r="Y43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="Z43" s="3">
         <v>29900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>28100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>37000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>34700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>37100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>28000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>30500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>29600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>32300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>30300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>107200</v>
+      </c>
+      <c r="E44" s="3">
         <v>96000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>101300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>98900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>92700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>106800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>112100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>116700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>116600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>127600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>124900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>90200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>72000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>84800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>84100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>84300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>88300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>122800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>115400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>114000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>100000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>111200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>119600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>113000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>104500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>107900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>121500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>127800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>106200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>131800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>145700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>13100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>11300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>11800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>12500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>11000</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="N45" s="3">
+        <v>9900</v>
+      </c>
+      <c r="O45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="P45" s="3">
+        <v>15400</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R45" s="3">
+        <v>9900</v>
+      </c>
+      <c r="S45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="T45" s="3">
         <v>11100</v>
       </c>
-      <c r="J45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>10700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>9900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>9200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>15400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>9300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>9900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>9800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>11100</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>14300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>15300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>26000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>18200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>18300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>19300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>230200</v>
+      </c>
+      <c r="E46" s="3">
         <v>243500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>249600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>243100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>261100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>263800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>273500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>277700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>298800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>305500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>343500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>355700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>361800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>349600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>333100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>290600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>294500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>280700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>311100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>362800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>374200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>369300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>360200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>370600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>374900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>378400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>378900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>372500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>393400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>391500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>413700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>443800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>442900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4322,109 +4426,115 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>174400</v>
+      </c>
+      <c r="E48" s="3">
         <v>189800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>204200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>218700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>189900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>212200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>229700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>244700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>210800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>222600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>235600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>244300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>196000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>212000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>255800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>272400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>266200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>286700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>298700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>289500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>242600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>254600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>271000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>94300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>99300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>102300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>105500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>109400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>120200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>122500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>124700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>126400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4524,8 +4634,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4625,8 +4738,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4726,109 +4842,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E52" s="3">
         <v>22300</v>
       </c>
-      <c r="E52" s="3">
-        <v>23300</v>
-      </c>
       <c r="F52" s="3">
-        <v>25000</v>
+        <v>23200</v>
       </c>
       <c r="G52" s="3">
-        <v>36400</v>
+        <v>23000</v>
       </c>
       <c r="H52" s="3">
-        <v>31700</v>
+        <v>24700</v>
       </c>
       <c r="I52" s="3">
-        <v>31400</v>
+        <v>21100</v>
       </c>
       <c r="J52" s="3">
+        <v>20700</v>
+      </c>
+      <c r="K52" s="3">
         <v>30800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>29100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>32700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>34300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>32700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>34400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>34100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>34200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>34800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>35000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>35200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>36100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>32700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4928,109 +5050,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>424400</v>
+      </c>
+      <c r="E54" s="3">
         <v>455600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>477100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>486800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>487400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>507700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>534600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>553100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>540500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>560800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>612000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>633800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>587200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>590800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>617900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>591500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>590900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>596400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>641000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>685000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>651200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>657400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>665000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>497900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>506900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>515100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>518500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>516100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>548400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>549000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>573600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>606300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>617600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5066,8 +5194,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5103,132 +5232,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E57" s="3">
         <v>84600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>87800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>86900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>84900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>88500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>95200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>91600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>106200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>109500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>92900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>71500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>82300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>73800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>75000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>54000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>44900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>68400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>69100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>67700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>66600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>84300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>72600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>74900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>69100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>82600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>88300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>74500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>83100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>105200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>45800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>51100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>55800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>61100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>51400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>49700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5254,18 +5387,18 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3">
         <v>30000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5281,8 +5414,8 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5305,233 +5438,242 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>89000</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>96800</v>
+        <v>600</v>
       </c>
       <c r="F59" s="3">
-        <v>100200</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>97300</v>
+        <v>900</v>
       </c>
       <c r="H59" s="3">
-        <v>75500</v>
+        <v>2000</v>
       </c>
       <c r="I59" s="3">
-        <v>97100</v>
+        <v>3600</v>
       </c>
       <c r="J59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K59" s="3">
         <v>111000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>108300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>107700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>129500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>134600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>121400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>120300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>108200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>101700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>100100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>109600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>130900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>117700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>111900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>112800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>56800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>65500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>63500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>61800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>56500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>60800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>63000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>61000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>66700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>59300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E60" s="3">
         <v>173600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>183800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>188000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>184200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>160400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>185600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>203000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>203400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>199300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>235700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>244100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>214300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>201400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>202600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>181900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>176700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>154000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>184500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>199300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>186800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>179600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>179300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>141100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>138100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>138400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>130900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>139100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>149100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>137500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>144100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>171900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>63200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>72300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>81800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>92000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>71100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>105400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>105800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5608,109 +5750,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>86900</v>
+        <v>14600</v>
       </c>
       <c r="E62" s="3">
-        <v>96400</v>
+        <v>14600</v>
       </c>
       <c r="F62" s="3">
-        <v>106500</v>
+        <v>14600</v>
       </c>
       <c r="G62" s="3">
-        <v>85800</v>
+        <v>14500</v>
       </c>
       <c r="H62" s="3">
-        <v>121700</v>
+        <v>14700</v>
       </c>
       <c r="I62" s="3">
-        <v>122200</v>
+        <v>16300</v>
       </c>
       <c r="J62" s="3">
+        <v>16400</v>
+      </c>
+      <c r="K62" s="3">
         <v>123600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>102300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>115700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>125600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>135400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>102000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>115600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>153500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>163000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>158000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>176200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>184800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>169200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>132700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>143100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>157200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>42600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>45400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>46300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>50600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>46800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>48900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>49700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5810,8 +5958,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5911,8 +6062,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6012,109 +6166,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>247300</v>
+      </c>
+      <c r="E66" s="3">
         <v>260500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>280200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>294500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>270100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>282100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>307900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>326500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>305700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>315000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>361400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>379600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>316400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>317000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>356000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>345000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>334700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>330200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>369300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>368500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>319500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>322700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>336500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>181100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>180700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>183800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>177200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>189700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>195900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>186400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>193800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>222400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>205900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6150,8 +6310,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6251,8 +6412,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6352,8 +6516,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6453,8 +6620,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6554,109 +6724,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E72" s="3">
         <v>66100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>69500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>64300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>91200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>100800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>103400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>104700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>114800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>124800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>131200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>134200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>151200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>154900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>144400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>129300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>139800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>150900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>158000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>203500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>220200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>224500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>220800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>210500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>221800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>228100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>240400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>225900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>252600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>264000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>282800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>288000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6756,8 +6932,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6857,8 +7036,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6958,109 +7140,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>177100</v>
+      </c>
+      <c r="E76" s="3">
         <v>195100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>196900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>192300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>217300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>225500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>226800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>226600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>234800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>245800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>250700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>254200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>270800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>273800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>261900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>246500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>256100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>266200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>271700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>316500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>331700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>334600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>328500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>316800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>326200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>331300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>341200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>326400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>352400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>362600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>379800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>383900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>411700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7160,215 +7348,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E80" s="2">
         <v>45507</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45416</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45325</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43862</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43771</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43680</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43589</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43498</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43407</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43316</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43225</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43134</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
-        <v>10400</v>
-      </c>
       <c r="F81" s="3">
-        <v>-22100</v>
+        <v>11000</v>
       </c>
       <c r="G81" s="3">
-        <v>-5700</v>
+        <v>-23400</v>
       </c>
       <c r="H81" s="3">
-        <v>5300</v>
+        <v>-6100</v>
       </c>
       <c r="I81" s="3">
-        <v>4200</v>
+        <v>1100</v>
       </c>
       <c r="J81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-27200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>32000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>20600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>29000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-15100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>21700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7404,109 +7601,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="E83" s="3">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F83" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G83" s="3">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="H83" s="3">
-        <v>4900</v>
+        <v>2900</v>
       </c>
       <c r="I83" s="3">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="J83" s="3">
         <v>2700</v>
       </c>
       <c r="K83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3600</v>
       </c>
       <c r="S83" s="3">
         <v>3600</v>
       </c>
       <c r="T83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="U83" s="3">
         <v>7500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>4000</v>
       </c>
       <c r="V83" s="3">
         <v>4000</v>
       </c>
       <c r="W83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X83" s="3">
         <v>3800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7606,8 +7807,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7707,8 +7911,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7808,8 +8015,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7909,8 +8119,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8010,109 +8223,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E89" s="3">
         <v>3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9900</v>
       </c>
-      <c r="H89" s="3">
-        <v>21600</v>
-      </c>
       <c r="I89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="J89" s="3">
         <v>9900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>82000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>44500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-48200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-71300</v>
-      </c>
-      <c r="V89" s="3">
-        <v>4100</v>
       </c>
       <c r="W89" s="3">
         <v>4100</v>
       </c>
       <c r="X89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>45200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>56500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>31600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>43400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>25900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-8800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8148,109 +8367,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-600</v>
       </c>
       <c r="Q91" s="3">
         <v>-600</v>
       </c>
       <c r="R91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-700</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8350,8 +8573,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8451,109 +8677,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17700</v>
       </c>
-      <c r="H94" s="3">
-        <v>23800</v>
-      </c>
       <c r="I94" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J94" s="3">
         <v>15300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>15800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>25900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>13600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-34200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-33100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>91000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>76900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>7900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-69900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>13100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>21000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>33600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>18800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>4000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8589,76 +8821,77 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3500</v>
       </c>
-      <c r="E96" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-3600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-7300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>100</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-8000</v>
       </c>
       <c r="U96" s="3">
         <v>-8000</v>
       </c>
       <c r="V96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-8100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-8200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-16300</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-8100</v>
       </c>
       <c r="Z96" s="3">
         <v>-8100</v>
@@ -8667,31 +8900,34 @@
         <v>-8100</v>
       </c>
       <c r="AB96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-8200</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-8300</v>
       </c>
       <c r="AE96" s="3">
         <v>-8300</v>
       </c>
       <c r="AF96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-17200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8791,8 +9027,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8892,8 +9131,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8993,8 +9235,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9002,123 +9247,126 @@
         <v>-3500</v>
       </c>
       <c r="E100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-5600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3300</v>
       </c>
-      <c r="H100" s="3">
-        <v>-9300</v>
-      </c>
       <c r="I100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J100" s="3">
         <v>-5600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-17600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>12400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-10100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-26300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-11400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-46500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9171,11 +9419,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -9189,111 +9437,117 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>8</v>
+      <c r="AH101" s="3">
+        <v>0</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30900</v>
       </c>
-      <c r="H102" s="3">
-        <v>36100</v>
-      </c>
       <c r="I102" s="3">
+        <v>16400</v>
+      </c>
+      <c r="J102" s="3">
         <v>19700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-39800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>30500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>5600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>14500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>CATO</t>
   </si>
@@ -656,469 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
         <v>45598</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45507</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45416</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45325</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43862</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43771</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43680</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43589</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43498</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43407</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43316</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43225</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43134</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>157900</v>
+      </c>
+      <c r="E8" s="3">
         <v>146200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>168600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>177100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>174900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>158300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>182900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>192100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>179000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>176600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>403600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>206700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>176200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>172200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>420800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>213100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>155400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>150800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>268900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>100700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>190900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>191500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>442900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>230400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>192400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>190000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>447200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>238300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>213000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>190300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>446700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>239700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>220400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E9" s="3">
         <v>103000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>109100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>112500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>117100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>105800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>117600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>122100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>121900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>123800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>264000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>132200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>109600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>104200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>239300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>123700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>107400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>109400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>216300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>83600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>123800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>118600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>266500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>136100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>127400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>123000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>272100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>142300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>141600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>124500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>287000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>145800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>155300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E10" s="3">
         <v>42800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>59100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>64200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>64800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>69500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>57100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>52800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>139600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>181500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>89400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>48000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>41400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>52600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>67100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>72900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>176400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>94300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>65000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>67000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>175100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>96000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>71400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>65800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>159700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>93900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>65100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>75700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1168,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1259,8 +1273,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,40 +1380,43 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1413,20 +1433,20 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>3800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2300</v>
-      </c>
-      <c r="U14" s="3">
-        <v>5300</v>
       </c>
       <c r="V14" s="3">
         <v>5300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>5300</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1443,8 +1463,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1467,8 +1487,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1476,13 +1499,13 @@
         <v>2700</v>
       </c>
       <c r="E15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F15" s="3">
         <v>2300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2500</v>
       </c>
       <c r="H15" s="3">
         <v>2500</v>
@@ -1491,88 +1514,91 @@
         <v>2500</v>
       </c>
       <c r="J15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K15" s="3">
         <v>2400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>3600</v>
       </c>
       <c r="T15" s="3">
         <v>3600</v>
       </c>
       <c r="U15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V15" s="3">
         <v>7500</v>
-      </c>
-      <c r="V15" s="3">
-        <v>4000</v>
       </c>
       <c r="W15" s="3">
         <v>4000</v>
       </c>
       <c r="X15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>3800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>7700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>9900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>5100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,216 +1632,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>173200</v>
+      </c>
+      <c r="E17" s="3">
         <v>163600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>169600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>171300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>188700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>170100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>181700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>186400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>184500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>188000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>390800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>195400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>182800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>169900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>379700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>190000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>169200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>164900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>320300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>140100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>194800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>187100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>406200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>205900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>197300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>188900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>415300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>212500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>222400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>191600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>425000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>214600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>244100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>207200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>41100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-51400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-39400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>36700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>31900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>25800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>21700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>25100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-23700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1852,8 +1885,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1863,205 +1897,211 @@
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>1400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>2300</v>
       </c>
       <c r="M20" s="3">
         <v>2300</v>
       </c>
       <c r="N20" s="3">
-        <v>400</v>
+        <v>2300</v>
       </c>
       <c r="O20" s="3">
         <v>400</v>
       </c>
       <c r="P20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>26800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-41100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-33500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>47300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>29400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>30800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>33900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>31100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-16600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2074,11 +2114,11 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
@@ -2086,47 +2126,47 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
@@ -2134,142 +2174,148 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>200</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>42300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>23800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-48600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-37500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>39600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>25600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>34100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>26600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>23900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>26100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2277,50 +2323,50 @@
         <v>300</v>
       </c>
       <c r="E24" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>600</v>
       </c>
       <c r="G24" s="3">
+        <v>600</v>
+      </c>
+      <c r="H24" s="3">
         <v>10900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -2331,49 +2377,52 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-9600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2476,216 +2525,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>34700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-48600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-37500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>33100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>21300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>29900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>23400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>22200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-12800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>32900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-47000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-36300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>20600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>21700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-12500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2788,8 +2846,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2820,8 +2881,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -2838,21 +2899,21 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>2600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>9700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>13000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>9100</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2862,24 +2923,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>500</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-12300</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2892,8 +2953,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2996,8 +3060,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,8 +3167,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3111,205 +3181,211 @@
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-2300</v>
       </c>
       <c r="M32" s="3">
         <v>-2300</v>
       </c>
       <c r="N32" s="3">
-        <v>-400</v>
+        <v>-2300</v>
       </c>
       <c r="O32" s="3">
         <v>-400</v>
       </c>
       <c r="P32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>32900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-34000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-27200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>20600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-15100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>21700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-12500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3412,221 +3488,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>32900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-34000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-27200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>20600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-15100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>21700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-12500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
         <v>45598</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45507</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45416</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45325</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43862</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43771</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43680</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43589</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43498</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43407</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43316</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43225</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43134</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,8 +3748,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,429 +3787,442 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E41" s="3">
         <v>20200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>56000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>29800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>36500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>26700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>37800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>71500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>78000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>78700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>77700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>52400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>47200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E42" s="3">
         <v>66000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>66300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>79000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>93600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>77200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>87800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>108700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>128500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>123400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>120000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>146000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>176100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>191500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>160900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>126400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>132600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>100400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>118000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>200400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>203300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>207400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>174400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>182700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>183200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>187100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>147100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>118800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>136200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>159900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>178900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>201200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E43" s="3">
         <v>24800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>56000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>51300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>55100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>52700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>47700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>39000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>30500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26100</v>
-      </c>
-      <c r="X43" s="3">
-        <v>27500</v>
       </c>
       <c r="Y43" s="3">
         <v>27500</v>
       </c>
       <c r="Z43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="AA43" s="3">
         <v>29900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>28100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>37000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>34700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>37100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>28000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>30500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>29600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>32300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>110700</v>
+      </c>
+      <c r="E44" s="3">
         <v>107200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>96000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>101300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>98600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>98900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>92700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>106800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>112100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>116700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>116600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>127600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>124900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>90200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>72000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>84800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>84100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>84300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>88300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>122800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>115400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>114000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>100000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>111200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>119600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>113000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>104500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>107900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>121500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>127800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>106200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>131800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>145700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>7400</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4143,190 +4242,196 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>10500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>14300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>15300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>26000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>20300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>18200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>18300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>19300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>223200</v>
+      </c>
+      <c r="E46" s="3">
         <v>230200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>249600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>243100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>261100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>263800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>273500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>277700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>298800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>305500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>343500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>355700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>361800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>349600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>333100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>290600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>294500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>280700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>311100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>362800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>374200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>369300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>360200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>370600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>374900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>378400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>378900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>372500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>393400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>391500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>413700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>443800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>442900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4336,24 +4441,24 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>800</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4429,112 +4534,118 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>209200</v>
+      </c>
+      <c r="E48" s="3">
         <v>174400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>189800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>204200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>218700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>189900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>212200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>229700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>244700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>210800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>222600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>235600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>244300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>196000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>212000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>255800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>272400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>266200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>286700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>298700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>289500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>242600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>254600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>271000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>94300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>99300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>102300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>105500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>109400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>120200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>122500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>124700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>126400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4637,8 +4748,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4741,8 +4855,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4845,112 +4962,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E52" s="3">
         <v>19800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>32900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>32700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>34300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>33000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>32700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>34400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>34100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>34200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>34800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>35000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>35200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>32700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5053,112 +5176,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>452400</v>
+      </c>
+      <c r="E54" s="3">
         <v>424400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>455600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>477100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>486800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>487400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>507700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>534600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>553100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>540500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>560800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>612000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>633800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>587200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>590800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>617900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>591500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>590900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>596400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>641000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>685000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>651200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>657400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>665000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>497900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>506900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>515100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>518500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>516100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>548400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>549000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>573600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>606300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>617600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5195,8 +5324,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5233,139 +5363,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>84200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>84600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>87000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>87800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>86900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>88500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>95200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>91600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>106200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>109500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>92900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>71500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>73800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>75000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>54000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>44900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>68400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>67700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>66600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>84300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>72600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>74900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>69100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>82600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>88300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>74500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>83100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>105200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E58" s="3">
         <v>45800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>51100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>55800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>51400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>49700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5390,18 +5524,18 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3">
         <v>30000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5417,8 +5551,8 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5441,243 +5575,252 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>111000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>108300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>107700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>129500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>134600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>121400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>129900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>120300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>108200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>101700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>100100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>109600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>130900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>117700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>111900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>112800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>56800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>65500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>63500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>61800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>56500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>60800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>63000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>61000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>66700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>59300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>188200</v>
+      </c>
+      <c r="E60" s="3">
         <v>169500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>173600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>183800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>188000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>184200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>160400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>185600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>203000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>203400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>199300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>235700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>244100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>214300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>201400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>202600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>181900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>176700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>154000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>184500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>199300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>186800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>179600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>179300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>141100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>138100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>138400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>130900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>139100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>149100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>137500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>144100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>171900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E61" s="3">
         <v>63200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>72300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>81800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>92000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>71100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>105400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>105800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5753,13 +5896,16 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14600</v>
+        <v>13500</v>
       </c>
       <c r="E62" s="3">
         <v>14600</v>
@@ -5768,97 +5914,100 @@
         <v>14600</v>
       </c>
       <c r="G62" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H62" s="3">
         <v>14500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>123600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>102300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>115700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>125600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>135400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>102000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>115600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>153500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>163000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>158000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>176200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>184800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>169200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>132700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>143100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>157200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>40000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>42600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>45400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>46300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>50600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>46800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>48900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>49700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>50500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>51900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6110,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6065,8 +6217,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6169,112 +6324,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>290100</v>
+      </c>
+      <c r="E66" s="3">
         <v>247300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>260500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>280200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>294500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>270100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>282100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>307900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>326500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>305700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>315000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>361400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>379600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>316400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>317000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>356000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>345000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>334700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>330200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>369300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>368500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>319500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>322700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>336500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>181100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>180700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>183800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>177200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>189700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>195900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>186400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>193800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>222400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>205900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6311,8 +6472,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6415,8 +6577,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6519,8 +6684,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6623,8 +6791,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6727,112 +6898,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>47400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>64300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>91200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>100800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>103400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>104700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>114800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>124800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>131200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>134200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>151200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>154900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>144400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>129300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>139800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>150900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>158000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>203500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>220200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>224500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>220800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>210500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>221800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>228100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>240400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>225900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>252600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>264000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>282800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>288000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>316000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6935,8 +7112,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7039,8 +7219,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7143,112 +7326,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E76" s="3">
         <v>177100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>195100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>196900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>192300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>217300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>225500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>226800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>226600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>234800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>245800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>250700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>254200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>270800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>273800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>261900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>246500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>256100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>266200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>271700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>316500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>331700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>334600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>328500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>316800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>326200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>331300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>341200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>326400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>352400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>362600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>379800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>383900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>411700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7351,221 +7540,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
         <v>45598</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45507</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45416</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45325</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43862</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43771</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43680</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43589</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43498</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43407</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43316</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43225</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43134</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>32900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-34000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-27200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>20600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-15100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>21700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-12500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7602,8 +7800,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7614,100 +7813,103 @@
         <v>2500</v>
       </c>
       <c r="F83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G83" s="3">
         <v>2400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2700</v>
       </c>
       <c r="K83" s="3">
         <v>2700</v>
       </c>
       <c r="L83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>3600</v>
       </c>
       <c r="T83" s="3">
         <v>3600</v>
       </c>
       <c r="U83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V83" s="3">
         <v>7500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>4000</v>
       </c>
       <c r="W83" s="3">
         <v>4000</v>
       </c>
       <c r="X83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>3800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7810,8 +8012,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7914,8 +8119,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8018,8 +8226,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8122,8 +8333,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8226,112 +8440,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>82000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>44500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-48200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-71300</v>
-      </c>
-      <c r="W89" s="3">
-        <v>4100</v>
       </c>
       <c r="X89" s="3">
         <v>4100</v>
       </c>
       <c r="Y89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Z89" s="3">
         <v>45200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>56500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>31600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>43400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>15600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>25900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-8800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8368,112 +8588,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-600</v>
       </c>
       <c r="R91" s="3">
         <v>-600</v>
       </c>
       <c r="S91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8576,8 +8800,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8680,112 +8907,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>14800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>8500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>15300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>10100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>25900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>13600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-64900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>6600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-33100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>91000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>76900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>7900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-69900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>13100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>21000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>33600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>18800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8822,13 +9055,14 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>3500</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
         <v>3500</v>
@@ -8849,52 +9083,52 @@
         <v>3500</v>
       </c>
       <c r="K96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-7300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>100</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-8000</v>
       </c>
       <c r="V96" s="3">
         <v>-8000</v>
       </c>
       <c r="W96" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-8100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-16300</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-8100</v>
       </c>
       <c r="AA96" s="3">
         <v>-8100</v>
@@ -8903,31 +9137,34 @@
         <v>-8100</v>
       </c>
       <c r="AC96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8200</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-8300</v>
       </c>
       <c r="AF96" s="3">
         <v>-8300</v>
       </c>
       <c r="AG96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-17200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-8900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9030,8 +9267,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9134,8 +9374,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9238,112 +9481,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-3500</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3">
         <v>-3500</v>
       </c>
       <c r="F100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G100" s="3">
         <v>-5600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-17600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>12400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-26300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-11400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-46500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9617,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9422,11 +9671,11 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -9440,114 +9689,120 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>8</v>
+      <c r="AI101" s="3">
+        <v>0</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>25200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-39800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>30500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>5600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10300</v>
       </c>
     </row>
